--- a/artfynd/A 66957-2021 artfynd.xlsx
+++ b/artfynd/A 66957-2021 artfynd.xlsx
@@ -769,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -875,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122596275</v>
+        <v>122596271</v>
       </c>
       <c r="B4" t="n">
-        <v>94263</v>
+        <v>79641</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2387</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>793022</v>
+        <v>792911</v>
       </c>
       <c r="R4" t="n">
-        <v>7443164</v>
+        <v>7443214</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,12 +981,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1087,22 +1087,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122596271</v>
+        <v>122596275</v>
       </c>
       <c r="B6" t="n">
-        <v>79641</v>
+        <v>94263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>792911</v>
+        <v>793022</v>
       </c>
       <c r="R6" t="n">
-        <v>7443214</v>
+        <v>7443164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 66957-2021 artfynd.xlsx
+++ b/artfynd/A 66957-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122596274</v>
+        <v>122596271</v>
       </c>
       <c r="B2" t="n">
-        <v>79766</v>
+        <v>79641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>792976</v>
+        <v>792911</v>
       </c>
       <c r="R2" t="n">
-        <v>7443157</v>
+        <v>7443214</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122596273</v>
+        <v>122596272</v>
       </c>
       <c r="B3" t="n">
-        <v>95784</v>
+        <v>79641</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>792972</v>
+        <v>792926</v>
       </c>
       <c r="R3" t="n">
-        <v>7443159</v>
+        <v>7443181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122596271</v>
+        <v>122596275</v>
       </c>
       <c r="B4" t="n">
-        <v>79641</v>
+        <v>94265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2387</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792911</v>
+        <v>793022</v>
       </c>
       <c r="R4" t="n">
-        <v>7443214</v>
+        <v>7443164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122596272</v>
+        <v>122596273</v>
       </c>
       <c r="B5" t="n">
-        <v>79641</v>
+        <v>95786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>792926</v>
+        <v>792972</v>
       </c>
       <c r="R5" t="n">
-        <v>7443181</v>
+        <v>7443159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122596275</v>
+        <v>122596274</v>
       </c>
       <c r="B6" t="n">
-        <v>94263</v>
+        <v>79766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2387</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>793022</v>
+        <v>792976</v>
       </c>
       <c r="R6" t="n">
-        <v>7443164</v>
+        <v>7443157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 66957-2021 artfynd.xlsx
+++ b/artfynd/A 66957-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122596275</v>
+        <v>122596271</v>
       </c>
       <c r="B2" t="n">
-        <v>94372</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2387</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>793022</v>
+        <v>792911</v>
       </c>
       <c r="R2" t="n">
-        <v>7443164</v>
+        <v>7443214</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122596271</v>
+        <v>122596272</v>
       </c>
       <c r="B3" t="n">
-        <v>79747</v>
+        <v>79751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>792911</v>
+        <v>792926</v>
       </c>
       <c r="R3" t="n">
-        <v>7443214</v>
+        <v>7443181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122596272</v>
+        <v>122596273</v>
       </c>
       <c r="B4" t="n">
-        <v>79747</v>
+        <v>95901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792926</v>
+        <v>792972</v>
       </c>
       <c r="R4" t="n">
-        <v>7443181</v>
+        <v>7443159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122596274</v>
+        <v>122596275</v>
       </c>
       <c r="B5" t="n">
-        <v>79872</v>
+        <v>94380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2387</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>792976</v>
+        <v>793022</v>
       </c>
       <c r="R5" t="n">
-        <v>7443157</v>
+        <v>7443164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122596273</v>
+        <v>122596274</v>
       </c>
       <c r="B6" t="n">
-        <v>95893</v>
+        <v>79876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>792972</v>
+        <v>792976</v>
       </c>
       <c r="R6" t="n">
-        <v>7443159</v>
+        <v>7443157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 66957-2021 artfynd.xlsx
+++ b/artfynd/A 66957-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122596271</v>
+        <v>122596274</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>79876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>792911</v>
+        <v>792976</v>
       </c>
       <c r="R2" t="n">
-        <v>7443214</v>
+        <v>7443157</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122596272</v>
+        <v>122596271</v>
       </c>
       <c r="B3" t="n">
         <v>79751</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>792926</v>
+        <v>792911</v>
       </c>
       <c r="R3" t="n">
-        <v>7443181</v>
+        <v>7443214</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122596275</v>
+        <v>122596272</v>
       </c>
       <c r="B5" t="n">
-        <v>94380</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2387</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>793022</v>
+        <v>792926</v>
       </c>
       <c r="R5" t="n">
-        <v>7443164</v>
+        <v>7443181</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122596274</v>
+        <v>122596275</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>94380</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>792976</v>
+        <v>793022</v>
       </c>
       <c r="R6" t="n">
-        <v>7443157</v>
+        <v>7443164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 66957-2021 artfynd.xlsx
+++ b/artfynd/A 66957-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122596271</v>
+        <v>122596275</v>
       </c>
       <c r="B3" t="n">
-        <v>79751</v>
+        <v>94382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>2387</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>792911</v>
+        <v>793022</v>
       </c>
       <c r="R3" t="n">
-        <v>7443214</v>
+        <v>7443164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122596273</v>
+        <v>122596272</v>
       </c>
       <c r="B4" t="n">
-        <v>95901</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792972</v>
+        <v>792926</v>
       </c>
       <c r="R4" t="n">
-        <v>7443159</v>
+        <v>7443181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122596272</v>
+        <v>122596273</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>95903</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>792926</v>
+        <v>792972</v>
       </c>
       <c r="R5" t="n">
-        <v>7443181</v>
+        <v>7443159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122596275</v>
+        <v>122596271</v>
       </c>
       <c r="B6" t="n">
-        <v>94380</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2387</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>793022</v>
+        <v>792911</v>
       </c>
       <c r="R6" t="n">
-        <v>7443164</v>
+        <v>7443214</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 66957-2021 artfynd.xlsx
+++ b/artfynd/A 66957-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122596274</v>
+        <v>122596272</v>
       </c>
       <c r="B2" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>792976</v>
+        <v>792926</v>
       </c>
       <c r="R2" t="n">
-        <v>7443157</v>
+        <v>7443181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122596275</v>
+        <v>122596274</v>
       </c>
       <c r="B3" t="n">
-        <v>94382</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2387</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>793022</v>
+        <v>792976</v>
       </c>
       <c r="R3" t="n">
-        <v>7443164</v>
+        <v>7443157</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122596272</v>
+        <v>122596275</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>94382</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2387</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792926</v>
+        <v>793022</v>
       </c>
       <c r="R4" t="n">
-        <v>7443181</v>
+        <v>7443164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122596273</v>
+        <v>122596271</v>
       </c>
       <c r="B5" t="n">
-        <v>95903</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>792972</v>
+        <v>792911</v>
       </c>
       <c r="R5" t="n">
-        <v>7443159</v>
+        <v>7443214</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122596271</v>
+        <v>122596273</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>95903</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>792911</v>
+        <v>792972</v>
       </c>
       <c r="R6" t="n">
-        <v>7443214</v>
+        <v>7443159</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 66957-2021 artfynd.xlsx
+++ b/artfynd/A 66957-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122596272</v>
+        <v>122596274</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>79876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>792926</v>
+        <v>792976</v>
       </c>
       <c r="R2" t="n">
-        <v>7443181</v>
+        <v>7443157</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122596274</v>
+        <v>122596272</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>792976</v>
+        <v>792926</v>
       </c>
       <c r="R3" t="n">
-        <v>7443157</v>
+        <v>7443181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122596275</v>
+        <v>122596273</v>
       </c>
       <c r="B4" t="n">
-        <v>94382</v>
+        <v>95911</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2387</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>793022</v>
+        <v>792972</v>
       </c>
       <c r="R4" t="n">
-        <v>7443164</v>
+        <v>7443159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122596273</v>
+        <v>122596275</v>
       </c>
       <c r="B6" t="n">
-        <v>95903</v>
+        <v>94390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>792972</v>
+        <v>793022</v>
       </c>
       <c r="R6" t="n">
-        <v>7443159</v>
+        <v>7443164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
